--- a/epics/1118/specs/Spec_example.xlsx
+++ b/epics/1118/specs/Spec_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viber\Desktop\Data Projects\data-quality-project\epics\1118\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C54F9F-3AE3-447E-9C3D-A1BF6B16CA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA67F49-DEC2-4178-8D7D-F08702B3BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14265" yWindow="5700" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40245" yWindow="2355" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROJECT" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="72">
   <si>
     <t>Table</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Label_X1</t>
   </si>
   <si>
-    <t>DescX1</t>
-  </si>
-  <si>
     <t>DefX1</t>
   </si>
   <si>
@@ -214,15 +211,6 @@
     <t>DefX4</t>
   </si>
   <si>
-    <t>DescX2</t>
-  </si>
-  <si>
-    <t>DescX3</t>
-  </si>
-  <si>
-    <t>DescX4</t>
-  </si>
-  <si>
     <t>Label_X2</t>
   </si>
   <si>
@@ -248,6 +236,9 @@
   </si>
   <si>
     <t>proj_id, column1</t>
+  </si>
+  <si>
+    <t>VARCHAR (40 000)</t>
   </si>
 </sst>
 </file>
@@ -629,7 +620,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -714,21 +705,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE571E1A-2F83-410E-9D92-A928C44AD5A7}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,53 +729,47 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>56</v>
@@ -797,139 +781,121 @@
         <v>58</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -975,13 +941,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1035,13 +1001,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>51</v>

--- a/epics/1118/specs/Spec_example.xlsx
+++ b/epics/1118/specs/Spec_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viber\Desktop\Data Projects\data-quality-project\epics\1118\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA67F49-DEC2-4178-8D7D-F08702B3BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E3E4B9-83D9-4775-9F2B-5933E0D56464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40245" yWindow="2355" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40455" yWindow="945" windowWidth="24945" windowHeight="14220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROJECT" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="74">
   <si>
     <t>Table</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Traitements ?</t>
   </si>
   <si>
-    <t>PROJECT</t>
-  </si>
-  <si>
     <t>proj_id</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>column1</t>
   </si>
   <si>
-    <t>Label_1</t>
-  </si>
-  <si>
     <t>Desc1</t>
   </si>
   <si>
@@ -100,9 +94,6 @@
     <t>column2</t>
   </si>
   <si>
-    <t>Label_2</t>
-  </si>
-  <si>
     <t>Desc2</t>
   </si>
   <si>
@@ -118,9 +109,6 @@
     <t>column3</t>
   </si>
   <si>
-    <t>Label_3</t>
-  </si>
-  <si>
     <t>Desc3</t>
   </si>
   <si>
@@ -136,9 +124,6 @@
     <t>column4</t>
   </si>
   <si>
-    <t>Label_4</t>
-  </si>
-  <si>
     <t>Desc4</t>
   </si>
   <si>
@@ -190,55 +175,76 @@
     <t>Une WBS appartient obligatoirement à un projet</t>
   </si>
   <si>
+    <t>columnX1</t>
+  </si>
+  <si>
+    <t>Label_X1</t>
+  </si>
+  <si>
+    <t>DefX1</t>
+  </si>
+  <si>
+    <t>DefX2</t>
+  </si>
+  <si>
+    <t>DefX3</t>
+  </si>
+  <si>
+    <t>DefX4</t>
+  </si>
+  <si>
+    <t>Label_X2</t>
+  </si>
+  <si>
+    <t>Label_X3</t>
+  </si>
+  <si>
+    <t>Label_X4</t>
+  </si>
+  <si>
+    <t>columnX2</t>
+  </si>
+  <si>
+    <t>columnX3</t>
+  </si>
+  <si>
+    <t>columnX4</t>
+  </si>
+  <si>
+    <t>test_id</t>
+  </si>
+  <si>
+    <t>proj_id, column1</t>
+  </si>
+  <si>
+    <t>VARCHAR (40 000)</t>
+  </si>
+  <si>
+    <t>Label_X5</t>
+  </si>
+  <si>
+    <t>Label_X6</t>
+  </si>
+  <si>
+    <t>label_1</t>
+  </si>
+  <si>
+    <t>label_2</t>
+  </si>
+  <si>
+    <t>label_3</t>
+  </si>
+  <si>
+    <t>label_4</t>
+  </si>
+  <si>
     <t>proj_id &amp; column1</t>
   </si>
   <si>
-    <t>columnX1</t>
-  </si>
-  <si>
-    <t>Label_X1</t>
-  </si>
-  <si>
-    <t>DefX1</t>
-  </si>
-  <si>
-    <t>DefX2</t>
-  </si>
-  <si>
-    <t>DefX3</t>
-  </si>
-  <si>
-    <t>DefX4</t>
-  </si>
-  <si>
-    <t>Label_X2</t>
-  </si>
-  <si>
-    <t>Label_X3</t>
-  </si>
-  <si>
-    <t>Label_X4</t>
-  </si>
-  <si>
-    <t>columnX2</t>
-  </si>
-  <si>
-    <t>columnX3</t>
-  </si>
-  <si>
-    <t>columnX4</t>
-  </si>
-  <si>
-    <t>test_id</t>
-  </si>
-  <si>
-    <t>CALENDAR</t>
-  </si>
-  <si>
-    <t>proj_id, column1</t>
-  </si>
-  <si>
-    <t>VARCHAR (40 000)</t>
+    <t>ipn_project</t>
+  </si>
+  <si>
+    <t>ipn_calendar</t>
   </si>
 </sst>
 </file>
@@ -573,132 +579,133 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -746,157 +753,157 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -921,33 +928,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -972,54 +979,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
